--- a/data/CReDEs/v4/dg_jrzl.xlsx
+++ b/data/CReDEs/v4/dg_jrzl.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\桌面\东肝\CReDEs\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1043A6CB-4AF4-44F8-ACA5-B87DD61903DB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9E8AB59-F6A1-472A-AD97-FDA6C8D15795}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135" xr2:uid="{B74AE3A5-8732-4451-BE98-354521947AF8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="179021"/>
+  <calcPr calcId="179021" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -85,10 +85,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>肿瘤范围</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>肿瘤个数</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -97,11 +93,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>填写符合描述的内容，若没有描述则为“未描述”</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>填写符合描述的内容，单位为"个"，若没有描述则为“未描述”</t>
+    <t>术后处理情况_肿瘤范围</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>请填写下列选项:左，右，弥漫性，未描述</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>请填写以下选项：无，有，未描述，若有则填写相应的内容，单位为“个”</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -521,6 +521,7 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="4" max="4" width="24.5" customWidth="1"/>
     <col min="5" max="5" width="23.875" customWidth="1"/>
     <col min="6" max="6" width="24.5" customWidth="1"/>
     <col min="7" max="7" width="27" customWidth="1"/>
@@ -566,7 +567,7 @@
         <v>13</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -586,7 +587,7 @@
         <v>13</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -600,13 +601,13 @@
         <v>14</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/data/CReDEs/v4/dg_jrzl.xlsx
+++ b/data/CReDEs/v4/dg_jrzl.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\桌面\东肝\CReDEs\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9E8AB59-F6A1-472A-AD97-FDA6C8D15795}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78BFCE74-066B-4F6B-9C62-7A1A599E6069}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135" xr2:uid="{B74AE3A5-8732-4451-BE98-354521947AF8}"/>
   </bookViews>
@@ -85,23 +85,23 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>请填写下列选项:无，可疑，存在，无报告,</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>术后处理情况_肿瘤范围</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>请填写下列选项:左，右，弥漫性，未描述</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>请填写以下选项：无，有，未描述，若有则填写相应的内容，单位为“个”</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>肿瘤个数</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>请填写下列选项:无，可疑，存在，无报告,</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>术后处理情况_肿瘤范围</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>请填写下列选项:左，右，弥漫性，未描述</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>请填写以下选项：无，有，未描述，若有则填写相应的内容，单位为“个”</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -521,6 +521,7 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="20.125" customWidth="1"/>
     <col min="4" max="4" width="24.5" customWidth="1"/>
     <col min="5" max="5" width="23.875" customWidth="1"/>
     <col min="6" max="6" width="24.5" customWidth="1"/>
@@ -567,7 +568,7 @@
         <v>13</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -581,13 +582,13 @@
         <v>11</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -601,7 +602,7 @@
         <v>14</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>13</v>
